--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>c.1582</t>
+          <t>environ 1582</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>c.1582</t>
+          <t>environ 1582</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>c.1582</t>
+          <t>environ 1582</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>c.1582</t>
+          <t>environ 1582</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>c.1618</t>
+          <t>environ 1618</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>c.1618</t>
+          <t>environ 1618</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>c.1593</t>
+          <t>environ 1593</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>c.1593</t>
+          <t>environ 1593</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>c.1593</t>
+          <t>environ 1593</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>c.1593</t>
+          <t>environ 1593</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>c.1597</t>
+          <t>environ 1597</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>c.1597</t>
+          <t>environ 1597</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>c.1597</t>
+          <t>environ 1597</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>c.1684</t>
+          <t>environ 1684</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>c.1684</t>
+          <t>environ 1684</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>c.1684</t>
+          <t>environ 1684</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>c.1600</t>
+          <t>environ 1600</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>c.1600</t>
+          <t>environ 1600</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>c.1600</t>
+          <t>environ 1600</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">

--- a/quizzes/peinture-17e.xlsx
+++ b/quizzes/peinture-17e.xlsx
@@ -2112,7 +2112,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>environ 1597</t>
+          <t>1597 environ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>environ 1597</t>
+          <t>1597 environ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>environ 1597</t>
+          <t>1597 environ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>environ 1684</t>
+          <t>1684 environ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>environ 1684</t>
+          <t>1684 environ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>environ 1684</t>
+          <t>1684 environ</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>environ 1582</t>
+          <t>1582 environ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>environ 1582</t>
+          <t>1582 environ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>environ 1582</t>
+          <t>1582 environ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>environ 1582</t>
+          <t>1582 environ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>environ 1618</t>
+          <t>1618 environ</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>environ 1618</t>
+          <t>1618 environ</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>environ 1593</t>
+          <t>1593 environ</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>environ 1593</t>
+          <t>1593 environ</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>environ 1593</t>
+          <t>1593 environ</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>environ 1593</t>
+          <t>1593 environ</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>environ 1600</t>
+          <t>1600 environ</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>environ 1600</t>
+          <t>1600 environ</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>environ 1600</t>
+          <t>1600 environ</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
